--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-11T06:08:14.344Z</t>
+    <t>2026-09-11T07:26:52.018Z</t>
   </si>
   <si>
     <t>Life Insurance : Buy Best Life Insurance Policy Online at Bajaj Life Insurance (Bajaj Allianz)</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-11T07:26:52.018Z</t>
+    <t>2026-09-11T08:07:44.017Z</t>
   </si>
   <si>
     <t>Life Insurance : Buy Best Life Insurance Policy Online at Bajaj Life Insurance (Bajaj Allianz)</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-11T08:07:44.017Z</t>
+    <t>2026-09-11T08:23:05.118Z</t>
   </si>
   <si>
     <t>Life Insurance : Buy Best Life Insurance Policy Online at Bajaj Life Insurance (Bajaj Allianz)</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-11T08:23:05.118Z</t>
+    <t>2026-09-11T08:43:55.963Z</t>
   </si>
   <si>
     <t>Life Insurance : Buy Best Life Insurance Policy Online at Bajaj Life Insurance (Bajaj Allianz)</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-11T08:43:55.963Z</t>
+    <t>2026-09-11T09:08:17.124Z</t>
   </si>
   <si>
     <t>Life Insurance : Buy Best Life Insurance Policy Online at Bajaj Life Insurance (Bajaj Allianz)</t>
